--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4403" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4402" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,7 +657,7 @@
     <t>remarquePatient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionCommentairePatient}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment}
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>consignesAgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionInstructionsAgent}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions}
 </t>
   </si>
   <si>
@@ -683,7 +683,7 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionStatus}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
 </t>
   </si>
   <si>
@@ -862,9 +862,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/CodeSystem/fr-core-identifier-type</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1329,7 +1326,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>
@@ -6346,46 +6343,44 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="Y35" s="2"/>
+      <c r="Z35" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6403,21 +6398,21 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6443,13 +6438,13 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6499,7 +6494,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6517,21 +6512,21 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6557,14 +6552,14 @@
         <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6574,46 +6569,46 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6631,21 +6626,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6671,14 +6666,14 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6727,7 +6722,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6745,21 +6740,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6782,19 +6777,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6843,7 +6838,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6861,21 +6856,21 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6901,16 +6896,16 @@
         <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6959,7 +6954,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6977,21 +6972,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7017,16 +7012,16 @@
         <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7039,43 +7034,43 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7093,21 +7088,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>322</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7133,13 +7128,13 @@
         <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7153,43 +7148,43 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7207,21 +7202,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7244,13 +7239,13 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7301,7 +7296,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7319,21 +7314,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7356,16 +7351,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7415,7 +7410,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7433,21 +7428,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7473,13 +7468,13 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7508,11 +7503,11 @@
         <v>240</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7529,7 +7524,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>89</v>
@@ -7544,24 +7539,24 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7584,16 +7579,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7643,7 +7638,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7672,10 +7667,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7784,10 +7779,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7898,14 +7893,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7927,10 +7922,10 @@
         <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>113</v>
@@ -7985,7 +7980,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8014,10 +8009,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8043,10 +8038,10 @@
         <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8076,11 +8071,11 @@
         <v>240</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8097,7 +8092,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -8126,10 +8121,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8152,13 +8147,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8209,7 +8204,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8238,10 +8233,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8267,10 +8262,10 @@
         <v>147</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8300,11 +8295,11 @@
         <v>151</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8321,7 +8316,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -8339,21 +8334,21 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8462,10 +8457,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8576,10 +8571,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8624,7 +8619,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -8663,7 +8658,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8681,21 +8676,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8721,13 +8716,13 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8777,7 +8772,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8795,21 +8790,21 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8835,14 +8830,14 @@
         <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8871,7 +8866,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8889,7 +8884,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8907,21 +8902,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8947,14 +8942,14 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9003,7 +8998,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9021,21 +9016,21 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9058,19 +9053,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9119,7 +9114,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9137,21 +9132,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9174,13 +9169,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9231,7 +9226,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9260,10 +9255,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9372,10 +9367,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9486,14 +9481,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9515,10 +9510,10 @@
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>113</v>
@@ -9573,7 +9568,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9602,10 +9597,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9631,10 +9626,10 @@
         <v>147</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9664,11 +9659,11 @@
         <v>151</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9685,7 +9680,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9714,10 +9709,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9740,13 +9735,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9797,7 +9792,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>89</v>
@@ -9826,10 +9821,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9855,13 +9850,13 @@
         <v>246</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9891,7 +9886,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9909,7 +9904,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9924,24 +9919,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9967,10 +9962,10 @@
         <v>246</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10000,11 +9995,11 @@
         <v>159</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10021,7 +10016,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10036,7 +10031,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>107</v>
@@ -10045,15 +10040,15 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10079,10 +10074,10 @@
         <v>246</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10112,11 +10107,11 @@
         <v>159</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10133,7 +10128,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10151,25 +10146,25 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10188,16 +10183,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10247,7 +10242,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10262,24 +10257,24 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10302,13 +10297,13 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10359,7 +10354,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10374,28 +10369,28 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10414,13 +10409,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10471,7 +10466,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10486,10 +10481,10 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -10500,10 +10495,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10526,13 +10521,13 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10583,7 +10578,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10598,24 +10593,24 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10724,10 +10719,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10838,14 +10833,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10867,10 +10862,10 @@
         <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>113</v>
@@ -10925,7 +10920,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10954,10 +10949,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10983,13 +10978,13 @@
         <v>246</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11018,10 +11013,10 @@
         <v>151</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11039,7 +11034,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11054,24 +11049,24 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11094,13 +11089,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11151,7 +11146,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11169,21 +11164,21 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11206,13 +11201,13 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11263,7 +11258,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11278,24 +11273,24 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11318,13 +11313,13 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11375,7 +11370,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11390,24 +11385,24 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11430,16 +11425,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11489,7 +11484,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11504,24 +11499,24 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11544,16 +11539,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11603,7 +11598,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11618,28 +11613,28 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11661,13 +11656,13 @@
         <v>246</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11696,11 +11691,11 @@
         <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
       </c>
@@ -11717,7 +11712,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11732,28 +11727,28 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AM82" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11772,16 +11767,16 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L83" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="M83" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11831,7 +11826,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11846,24 +11841,24 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="AM83" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11886,13 +11881,13 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11943,7 +11938,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11961,7 +11956,7 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -11972,10 +11967,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12084,10 +12079,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12198,14 +12193,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12227,10 +12222,10 @@
         <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>113</v>
@@ -12285,7 +12280,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12314,14 +12309,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12340,16 +12335,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="N88" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12399,7 +12394,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>89</v>
@@ -12414,24 +12409,24 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AL88" t="s" s="2">
+      <c r="AM88" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12457,10 +12452,10 @@
         <v>246</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12490,11 +12485,11 @@
         <v>173</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12511,7 +12506,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12540,10 +12535,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12566,13 +12561,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12623,7 +12618,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12641,7 +12636,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12652,10 +12647,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12678,16 +12673,16 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12737,7 +12732,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12755,7 +12750,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12766,10 +12761,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12792,16 +12787,16 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12851,7 +12846,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12869,7 +12864,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -12880,10 +12875,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12992,10 +12987,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13106,14 +13101,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13135,10 +13130,10 @@
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>113</v>
@@ -13193,7 +13188,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13222,10 +13217,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13251,10 +13246,10 @@
         <v>225</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13305,7 +13300,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13329,15 +13324,15 @@
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13446,10 +13441,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13560,10 +13555,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13676,10 +13671,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13708,7 +13703,7 @@
         <v>247</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>249</v>
@@ -13790,10 +13785,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13819,65 +13814,65 @@
         <v>131</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N101" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O101" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T101" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13895,21 +13890,21 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>322</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13935,13 +13930,13 @@
         <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13955,43 +13950,43 @@
         <v>81</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14009,21 +14004,21 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14046,13 +14041,13 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14103,7 +14098,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14121,21 +14116,21 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14158,16 +14153,16 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14217,7 +14212,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14235,21 +14230,21 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14272,13 +14267,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14329,7 +14324,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14347,7 +14342,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14358,10 +14353,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14387,10 +14382,10 @@
         <v>246</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14420,11 +14415,11 @@
         <v>173</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z106" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
       </c>
@@ -14441,7 +14436,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14459,21 +14454,21 @@
         <v>81</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14499,10 +14494,10 @@
         <v>246</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14532,11 +14527,11 @@
         <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
       </c>
@@ -14553,7 +14548,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14577,15 +14572,15 @@
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14611,16 +14606,16 @@
         <v>246</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -14648,11 +14643,11 @@
         <v>159</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
       </c>
@@ -14669,7 +14664,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14687,21 +14682,21 @@
         <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>591</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14727,10 +14722,10 @@
         <v>246</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14760,11 +14755,11 @@
         <v>173</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>81</v>
       </c>
@@ -14781,7 +14776,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14799,21 +14794,21 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>598</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14839,10 +14834,10 @@
         <v>246</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14872,11 +14867,11 @@
         <v>173</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
       </c>
@@ -14893,7 +14888,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14911,21 +14906,21 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>605</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14948,13 +14943,13 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15005,7 +15000,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15023,21 +15018,21 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>610</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15063,10 +15058,10 @@
         <v>246</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15097,7 +15092,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15115,7 +15110,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15133,21 +15128,21 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>616</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15170,16 +15165,16 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15229,7 +15224,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15247,7 +15242,7 @@
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>81</v>
@@ -15258,10 +15253,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15370,10 +15365,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15484,14 +15479,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15513,10 +15508,10 @@
         <v>110</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>113</v>
@@ -15571,7 +15566,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15600,10 +15595,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15626,13 +15621,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15683,7 +15678,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>89</v>
@@ -15698,24 +15693,24 @@
         <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AL117" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM117" t="s" s="2">
+      <c r="AN117" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>631</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15741,13 +15736,13 @@
         <v>169</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15776,11 +15771,11 @@
         <v>240</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="Z118" t="s" s="2">
-        <v>637</v>
-      </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
       </c>
@@ -15797,7 +15792,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15815,7 +15810,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
@@ -15826,10 +15821,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15855,13 +15850,13 @@
         <v>246</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15891,7 +15886,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -15909,7 +15904,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15938,10 +15933,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15964,13 +15959,13 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16021,7 +16016,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16039,7 +16034,7 @@
         <v>81</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16050,10 +16045,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16076,13 +16071,13 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16133,7 +16128,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16148,24 +16143,24 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AL121" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>651</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16188,16 +16183,16 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16247,7 +16242,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16262,10 +16257,10 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-encounter-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-encounter-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,7 +657,7 @@
     <t>remarquePatient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment}
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>consignesAgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions}
 </t>
   </si>
   <si>
@@ -683,7 +683,7 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
@@ -1211,7 +1211,7 @@
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -1490,7 +1490,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr)
+    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr)
 </t>
   </si>
   <si>
@@ -2403,7 +2403,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1326,7 +1326,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-encounter-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-encounter-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,7 +657,7 @@
     <t>remarquePatient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment}
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>consignesAgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions}
 </t>
   </si>
   <si>
@@ -683,7 +683,7 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
@@ -1211,7 +1211,7 @@
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -1490,7 +1490,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr)
+    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr)
 </t>
   </si>
   <si>
@@ -2403,7 +2403,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4402" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4402" uniqueCount="660">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,17 +683,23 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/statut-preadmission-fr}
 </t>
   </si>
   <si>
+    <t>Extension Statut Pré-admission</t>
+  </si>
+  <si>
+    <t>Extension transportant les statuts spécifiques de la pré-admission.</t>
+  </si>
+  <si>
     <t>Encounter.extension:consentements</t>
   </si>
   <si>
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-extension}
 </t>
   </si>
   <si>
@@ -1211,7 +1217,7 @@
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -4846,10 +4852,10 @@
         <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4929,13 +4935,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>81</v>
@@ -4957,13 +4963,13 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5043,10 +5049,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5072,16 +5078,16 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5130,7 +5136,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5159,10 +5165,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5185,13 +5191,13 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5242,7 +5248,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5257,24 +5263,24 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5383,10 +5389,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5497,10 +5503,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5526,16 +5532,16 @@
         <v>169</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5545,7 +5551,7 @@
         <v>81</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>81</v>
@@ -5560,13 +5566,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5584,7 +5590,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5602,7 +5608,7 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -5613,10 +5619,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5639,19 +5645,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5680,7 +5686,7 @@
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5698,7 +5704,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5716,21 +5722,21 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5839,10 +5845,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5953,10 +5959,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5982,16 +5988,16 @@
         <v>147</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6040,7 +6046,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6058,21 +6064,21 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6181,10 +6187,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6295,10 +6301,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6324,16 +6330,16 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6358,11 +6364,11 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6380,7 +6386,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6398,21 +6404,21 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6438,13 +6444,13 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6494,7 +6500,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6512,21 +6518,21 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6552,14 +6558,14 @@
         <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6569,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6608,7 +6614,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6626,21 +6632,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6666,14 +6672,14 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6722,7 +6728,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6740,21 +6746,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6777,19 +6783,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6838,7 +6844,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6856,21 +6862,21 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6896,16 +6902,16 @@
         <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6954,7 +6960,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6972,21 +6978,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7012,16 +7018,16 @@
         <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7034,7 +7040,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7070,7 +7076,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7088,21 +7094,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7128,13 +7134,13 @@
         <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7148,7 +7154,7 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>81</v>
@@ -7184,7 +7190,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7202,21 +7208,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7239,13 +7245,13 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7296,7 +7302,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7314,21 +7320,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7351,16 +7357,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7410,7 +7416,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7428,21 +7434,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7468,13 +7474,13 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7500,13 +7506,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7524,7 +7530,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>89</v>
@@ -7539,24 +7545,24 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7579,16 +7585,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7638,7 +7644,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7667,10 +7673,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7779,10 +7785,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7893,14 +7899,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7922,16 +7928,16 @@
         <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7980,7 +7986,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8009,10 +8015,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8038,10 +8044,10 @@
         <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8068,13 +8074,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8092,7 +8098,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -8121,10 +8127,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8147,13 +8153,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8204,7 +8210,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8233,10 +8239,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8262,10 +8268,10 @@
         <v>147</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8295,10 +8301,10 @@
         <v>151</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8316,7 +8322,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -8334,21 +8340,21 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8457,10 +8463,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8571,10 +8577,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8600,16 +8606,16 @@
         <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8619,7 +8625,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -8658,7 +8664,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8676,21 +8682,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8716,13 +8722,13 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8772,7 +8778,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8790,21 +8796,21 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8830,14 +8836,14 @@
         <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8862,11 +8868,11 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8884,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8902,21 +8908,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8942,14 +8948,14 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8998,7 +9004,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9016,21 +9022,21 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9053,19 +9059,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9114,7 +9120,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9132,21 +9138,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9169,13 +9175,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9226,7 +9232,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9255,10 +9261,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9367,10 +9373,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9481,14 +9487,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9510,16 +9516,16 @@
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9568,7 +9574,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9597,10 +9603,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9626,10 +9632,10 @@
         <v>147</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9659,10 +9665,10 @@
         <v>151</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9680,7 +9686,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9709,10 +9715,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9735,13 +9741,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9792,7 +9798,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>89</v>
@@ -9821,10 +9827,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9847,16 +9853,16 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9886,7 +9892,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9904,7 +9910,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9919,24 +9925,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9959,13 +9965,13 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9995,10 +10001,10 @@
         <v>159</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10016,7 +10022,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10031,7 +10037,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>107</v>
@@ -10040,15 +10046,15 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10071,13 +10077,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10107,28 +10113,28 @@
         <v>159</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10146,25 +10152,25 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10183,16 +10189,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10242,7 +10248,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10257,24 +10263,24 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10297,13 +10303,13 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10354,7 +10360,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10369,28 +10375,28 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10409,13 +10415,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10466,7 +10472,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10481,10 +10487,10 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -10495,10 +10501,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10521,13 +10527,13 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10578,7 +10584,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10593,24 +10599,24 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10719,10 +10725,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10833,14 +10839,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10862,16 +10868,16 @@
         <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10920,7 +10926,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10949,10 +10955,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10975,16 +10981,16 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11013,28 +11019,28 @@
         <v>151</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11049,24 +11055,24 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11089,13 +11095,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11146,7 +11152,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11164,21 +11170,21 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11201,13 +11207,13 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11258,7 +11264,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11273,24 +11279,24 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11313,13 +11319,13 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11370,7 +11376,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11385,24 +11391,24 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11425,16 +11431,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11484,7 +11490,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11499,24 +11505,24 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11539,16 +11545,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11598,7 +11604,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11613,28 +11619,28 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11653,16 +11659,16 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11691,10 +11697,10 @@
         <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -11712,7 +11718,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11727,28 +11733,28 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11767,16 +11773,16 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11826,7 +11832,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11841,24 +11847,24 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11881,13 +11887,13 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11938,7 +11944,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11956,7 +11962,7 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -11967,10 +11973,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12079,10 +12085,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12193,14 +12199,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12222,16 +12228,16 @@
         <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12280,7 +12286,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12309,14 +12315,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12335,16 +12341,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12394,7 +12400,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>89</v>
@@ -12409,24 +12415,24 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12449,13 +12455,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12485,10 +12491,10 @@
         <v>173</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12506,7 +12512,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12535,10 +12541,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12561,13 +12567,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12618,7 +12624,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12636,7 +12642,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12647,10 +12653,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12673,16 +12679,16 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12732,7 +12738,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12750,7 +12756,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12761,10 +12767,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12787,16 +12793,16 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12846,7 +12852,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12864,7 +12870,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -12875,10 +12881,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12987,10 +12993,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13101,14 +13107,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13130,16 +13136,16 @@
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13188,7 +13194,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13217,10 +13223,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13243,13 +13249,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13300,7 +13306,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13318,21 +13324,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13441,10 +13447,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13555,10 +13561,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13584,16 +13590,16 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -13618,13 +13624,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -13642,7 +13648,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13660,7 +13666,7 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
@@ -13671,10 +13677,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13697,19 +13703,19 @@
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -13738,7 +13744,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -13756,7 +13762,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13774,21 +13780,21 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13814,29 +13820,29 @@
         <v>131</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>81</v>
@@ -13872,7 +13878,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13890,21 +13896,21 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13930,13 +13936,13 @@
         <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13950,7 +13956,7 @@
         <v>81</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>81</v>
@@ -13986,7 +13992,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14004,21 +14010,21 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14041,13 +14047,13 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14098,7 +14104,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14116,21 +14122,21 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14153,16 +14159,16 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14212,7 +14218,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14230,21 +14236,21 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14267,13 +14273,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14324,7 +14330,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14342,7 +14348,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14353,10 +14359,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14379,13 +14385,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14415,10 +14421,10 @@
         <v>173</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14436,7 +14442,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14454,21 +14460,21 @@
         <v>81</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14491,13 +14497,13 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14527,10 +14533,10 @@
         <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14548,7 +14554,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14572,15 +14578,15 @@
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14603,19 +14609,19 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -14643,10 +14649,10 @@
         <v>159</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -14664,7 +14670,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14682,21 +14688,21 @@
         <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14719,13 +14725,13 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14755,10 +14761,10 @@
         <v>173</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>81</v>
@@ -14776,7 +14782,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14794,21 +14800,21 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14831,13 +14837,13 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14867,10 +14873,10 @@
         <v>173</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
@@ -14888,7 +14894,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14906,21 +14912,21 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14943,13 +14949,13 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15000,7 +15006,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15018,21 +15024,21 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15055,13 +15061,13 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15092,7 +15098,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15110,7 +15116,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15128,21 +15134,21 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15165,16 +15171,16 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15224,7 +15230,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15242,7 +15248,7 @@
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>81</v>
@@ -15253,10 +15259,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15365,10 +15371,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15479,14 +15485,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15508,16 +15514,16 @@
         <v>110</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -15566,7 +15572,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15595,10 +15601,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15621,13 +15627,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15678,7 +15684,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>89</v>
@@ -15693,24 +15699,24 @@
         <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15736,13 +15742,13 @@
         <v>169</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15768,13 +15774,13 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -15792,7 +15798,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15810,7 +15816,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
@@ -15821,10 +15827,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15847,16 +15853,16 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15886,7 +15892,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -15904,7 +15910,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15933,10 +15939,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15959,13 +15965,13 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16016,7 +16022,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16034,7 +16040,7 @@
         <v>81</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16045,10 +16051,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16071,13 +16077,13 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16128,7 +16134,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16143,24 +16149,24 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16183,16 +16189,16 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16242,7 +16248,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16257,10 +16263,10 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$123</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4402" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4438" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FHIR pour un encounter lié à une préadmission</t>
+    <t>Profil Encounter pour une préadmission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -661,7 +661,10 @@
 </t>
   </si>
   <si>
-    <t>Remarque du patient</t>
+    <t>Remarque patient</t>
+  </si>
+  <si>
+    <t>Remarque libre saisie par le patient à destination de l’agent administratif</t>
   </si>
   <si>
     <t>Encounter.extension:consignesAgent</t>
@@ -674,7 +677,10 @@
 </t>
   </si>
   <si>
-    <t>Consignes de l'agent administratif</t>
+    <t>Consignes agent</t>
+  </si>
+  <si>
+    <t>Consignes à destination du patient, fournies par l'agent administratif</t>
   </si>
   <si>
     <t>Encounter.extension:preadmissionStatus</t>
@@ -687,10 +693,10 @@
 </t>
   </si>
   <si>
-    <t>Extension Statut Pré-admission</t>
-  </si>
-  <si>
-    <t>Extension transportant les statuts spécifiques de la pré-admission.</t>
+    <t>Statut de préadmission</t>
+  </si>
+  <si>
+    <t>Statut de pré-admission</t>
   </si>
   <si>
     <t>Encounter.extension:consentements</t>
@@ -703,10 +709,26 @@
 </t>
   </si>
   <si>
-    <t>Consentement lié au rendez-vous</t>
-  </si>
-  <si>
-    <t>Référence vers un ou plusieurs consentements donnés dans le cadre de la préadmission.</t>
+    <t>Consentements</t>
+  </si>
+  <si>
+    <t>Consentement lié à la préadmission</t>
+  </si>
+  <si>
+    <t>Encounter.extension:questionnaire</t>
+  </si>
+  <si>
+    <t>questionnaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
+</t>
+  </si>
+  <si>
+    <t>Questionnaire libre lié à la préadmission</t>
+  </si>
+  <si>
+    <t>Référence vers un ou plusieurs QuestionnaireResponse remplis dans le cadre de la préadmission.</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -1208,16 +1230,13 @@
     <t>Encounter.class.system</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ActCode</t>
-  </si>
-  <si>
     <t>Encounter.class.version</t>
   </si>
   <si>
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -2381,7 +2400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN122"/>
+  <dimension ref="A1:AN123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.34765625" customWidth="true" bestFit="true"/>
@@ -4627,7 +4646,7 @@
         <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4707,13 +4726,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>81</v>
@@ -4735,13 +4754,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4821,13 +4840,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
@@ -4849,13 +4868,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4935,13 +4954,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>81</v>
@@ -4963,13 +4982,13 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5049,14 +5068,16 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5069,26 +5090,22 @@
         <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -5136,7 +5153,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5154,7 +5171,7 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
@@ -5165,42 +5182,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -5248,7 +5269,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5260,27 +5281,27 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>233</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5288,10 +5309,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5300,16 +5321,16 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>104</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5360,50 +5381,50 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5415,17 +5436,15 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5462,31 +5481,31 @@
         <v>81</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5503,46 +5522,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5551,7 +5568,7 @@
         <v>81</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>81</v>
@@ -5566,63 +5583,63 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5630,7 +5647,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5639,25 +5656,25 @@
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5667,7 +5684,7 @@
         <v>81</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>81</v>
@@ -5682,11 +5699,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5704,7 +5723,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5722,21 +5741,21 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>255</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5744,7 +5763,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>
@@ -5756,19 +5775,23 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5792,13 +5815,11 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5816,7 +5837,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5828,38 +5849,38 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5871,17 +5892,15 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5918,31 +5937,31 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5959,14 +5978,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5982,23 +6001,21 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6034,19 +6051,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>117</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6058,27 +6075,27 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>264</v>
+        <v>107</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>265</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6089,7 +6106,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -6098,19 +6115,23 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6158,50 +6179,50 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6213,17 +6234,15 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6260,31 +6279,31 @@
         <v>81</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -6301,21 +6320,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6324,23 +6343,21 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6364,61 +6381,63 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>117</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6441,18 +6460,20 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6476,13 +6497,11 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6555,7 +6574,7 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>284</v>
@@ -6563,10 +6582,10 @@
       <c r="M37" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>286</v>
       </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6575,46 +6594,46 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6632,21 +6651,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6669,17 +6688,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6689,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6783,19 +6802,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6844,7 +6861,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6862,21 +6879,21 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6899,19 +6916,19 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>306</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6960,7 +6977,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6978,21 +6995,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7000,7 +7017,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -7015,19 +7032,19 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7040,7 +7057,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7076,7 +7093,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7094,21 +7111,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7131,18 +7148,20 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7154,43 +7173,43 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7208,21 +7227,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7230,7 +7249,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -7245,15 +7264,17 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7266,7 +7287,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7365,9 +7386,7 @@
       <c r="M44" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7416,7 +7435,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7434,21 +7453,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7456,22 +7475,22 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>348</v>
@@ -7506,34 +7525,34 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AG45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>89</v>
@@ -7545,24 +7564,24 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7570,31 +7589,31 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7620,13 +7639,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>81</v>
+        <v>358</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7644,13 +7663,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -7659,24 +7678,24 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>361</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7687,7 +7706,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7699,15 +7718,17 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>104</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7756,19 +7777,19 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>106</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7785,21 +7806,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7811,17 +7832,15 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7870,19 +7889,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7899,14 +7918,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7919,26 +7938,24 @@
         <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O49" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7986,7 +8003,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8004,7 +8021,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8015,42 +8032,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8074,13 +8095,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8098,25 +8119,25 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -8127,10 +8148,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8153,13 +8174,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>333</v>
+        <v>169</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8186,13 +8207,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>81</v>
+        <v>358</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8210,7 +8231,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8239,10 +8260,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8256,22 +8277,22 @@
         <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>147</v>
+        <v>340</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8298,31 +8319,31 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -8340,21 +8361,21 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>378</v>
+        <v>107</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8362,28 +8383,28 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>104</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>105</v>
+        <v>382</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8410,13 +8431,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8434,10 +8455,10 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>106</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>89</v>
@@ -8446,38 +8467,38 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8489,17 +8510,15 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8536,31 +8555,31 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8577,21 +8596,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8600,23 +8619,21 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8625,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -8652,51 +8669,51 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>273</v>
+        <v>117</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8704,7 +8721,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8719,18 +8736,20 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8807,10 +8826,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8818,7 +8837,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8833,7 +8852,7 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>284</v>
@@ -8841,10 +8860,10 @@
       <c r="M57" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>286</v>
       </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8868,11 +8887,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8890,7 +8911,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8908,21 +8929,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8930,7 +8951,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8945,17 +8966,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8980,13 +9001,11 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9033,10 +9052,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9059,19 +9078,17 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9120,7 +9137,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9138,21 +9155,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9163,7 +9180,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9172,19 +9189,23 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>391</v>
+        <v>307</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9232,13 +9253,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9250,21 +9271,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>312</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9275,7 +9296,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9287,13 +9308,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9344,19 +9365,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>106</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9373,21 +9394,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9399,17 +9420,15 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9458,19 +9477,19 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9487,14 +9506,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9507,26 +9526,24 @@
         <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O63" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9574,7 +9591,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9592,7 +9609,7 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -9603,42 +9620,46 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9662,13 +9683,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9686,25 +9707,25 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
@@ -9715,10 +9736,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9741,13 +9762,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>333</v>
+        <v>147</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9774,13 +9795,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9798,7 +9819,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>89</v>
@@ -9827,10 +9848,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9838,7 +9859,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9850,20 +9871,18 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9888,11 +9907,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9910,13 +9931,13 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
@@ -9925,24 +9946,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>408</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9965,15 +9986,17 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10000,11 +10023,9 @@
       <c r="X67" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="Y67" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10022,13 +10043,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -10037,13 +10058,13 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>414</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>415</v>
@@ -10074,10 +10095,10 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>417</v>
@@ -10113,10 +10134,10 @@
         <v>159</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10149,28 +10170,28 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10186,20 +10207,18 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>425</v>
+        <v>255</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10224,13 +10243,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10248,7 +10267,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10263,35 +10282,35 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10303,15 +10322,17 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L70" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10360,13 +10381,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -10375,28 +10396,28 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10412,16 +10433,16 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10472,7 +10493,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10487,28 +10508,28 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10518,22 +10539,22 @@
         <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>358</v>
+        <v>448</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10584,7 +10605,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10599,16 +10620,16 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10627,25 +10648,25 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>104</v>
+        <v>454</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>105</v>
+        <v>455</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10696,50 +10717,50 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>106</v>
+        <v>453</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>107</v>
+        <v>457</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -10751,17 +10772,15 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10810,19 +10829,19 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -10839,14 +10858,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10859,26 +10878,24 @@
         <v>81</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O75" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -10926,7 +10943,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10944,7 +10961,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10955,14 +10972,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10975,24 +10992,26 @@
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>248</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>373</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>374</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11016,13 +11035,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>458</v>
+        <v>81</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11040,7 +11059,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11052,27 +11071,27 @@
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>462</v>
+        <v>192</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11083,7 +11102,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11092,18 +11111,20 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>333</v>
+        <v>255</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11128,13 +11149,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11152,13 +11173,13 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
@@ -11167,24 +11188,24 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11204,10 +11225,10 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>470</v>
+        <v>340</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>471</v>
@@ -11264,7 +11285,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11279,24 +11300,24 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>476</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11319,13 +11340,13 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11376,13 +11397,13 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
@@ -11391,13 +11412,13 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>482</v>
@@ -11416,32 +11437,30 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K80" t="s" s="2">
-        <v>333</v>
+        <v>484</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N80" t="s" s="2">
         <v>486</v>
       </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11515,7 @@
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>81</v>
@@ -11505,24 +11524,24 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>490</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11530,13 +11549,13 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>81</v>
@@ -11545,16 +11564,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11604,7 +11623,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11619,35 +11638,35 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -11656,19 +11675,19 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>248</v>
+        <v>498</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11694,13 +11713,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -11718,13 +11737,13 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
@@ -11733,28 +11752,28 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11773,16 +11792,16 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>510</v>
+        <v>255</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11808,13 +11827,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11832,7 +11851,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11847,28 +11866,28 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11887,15 +11906,17 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>358</v>
+        <v>516</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11944,7 +11965,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11959,24 +11980,24 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11987,7 +12008,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -11996,16 +12017,16 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>104</v>
+        <v>519</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>105</v>
+        <v>520</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12056,25 +12077,25 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>106</v>
+        <v>518</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>107</v>
+        <v>521</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -12085,21 +12106,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12111,17 +12132,15 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -12170,19 +12189,19 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
@@ -12199,14 +12218,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12219,26 +12238,24 @@
         <v>81</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O87" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12286,7 +12303,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12304,7 +12321,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -12315,44 +12332,46 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>521</v>
+        <v>110</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>522</v>
+        <v>373</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>523</v>
+        <v>374</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12400,47 +12419,47 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>525</v>
+        <v>192</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>89</v>
@@ -12452,10 +12471,10 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>248</v>
+        <v>527</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>528</v>
@@ -12463,7 +12482,9 @@
       <c r="M89" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12488,13 +12509,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>531</v>
+        <v>81</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12512,10 +12533,10 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>89</v>
@@ -12527,24 +12548,24 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>107</v>
+        <v>531</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12567,7 +12588,7 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>533</v>
+        <v>255</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>534</v>
@@ -12600,13 +12621,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>81</v>
+        <v>537</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12624,7 +12645,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12642,7 +12663,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12653,10 +12674,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12679,17 +12700,15 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N91" t="s" s="2">
         <v>541</v>
       </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -12738,13 +12757,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -12793,16 +12812,16 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>358</v>
+        <v>544</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12858,7 +12877,7 @@
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>81</v>
@@ -12870,7 +12889,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -12881,10 +12900,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12907,15 +12926,17 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>104</v>
+        <v>550</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12964,7 +12985,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>106</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12976,13 +12997,13 @@
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>107</v>
+        <v>553</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -12993,21 +13014,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13019,17 +13040,15 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13078,19 +13097,19 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13107,14 +13126,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13127,26 +13146,24 @@
         <v>81</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13194,7 +13211,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13212,7 +13229,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -13223,42 +13240,46 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>552</v>
+        <v>373</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13306,39 +13327,39 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>551</v>
+        <v>375</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13361,13 +13382,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>103</v>
+        <v>234</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>104</v>
+        <v>558</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>105</v>
+        <v>559</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13418,7 +13439,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>106</v>
+        <v>557</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13430,38 +13451,38 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>81</v>
+        <v>560</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
@@ -13473,17 +13494,15 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13520,31 +13539,31 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>81</v>
@@ -13561,46 +13580,44 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -13624,63 +13641,63 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13688,7 +13705,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>89</v>
@@ -13697,25 +13714,25 @@
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>559</v>
+        <v>245</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -13740,11 +13757,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -13762,7 +13781,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13780,21 +13799,21 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>255</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13817,32 +13836,32 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>316</v>
+        <v>256</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>81</v>
@@ -13854,13 +13873,11 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -13878,7 +13895,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>321</v>
+        <v>261</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13896,21 +13913,21 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>323</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13933,66 +13950,68 @@
         <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14010,21 +14029,21 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14032,7 +14051,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14047,15 +14066,17 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M103" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14068,7 +14089,7 @@
         <v>81</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>81</v>
@@ -14133,10 +14154,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14167,9 +14188,7 @@
       <c r="M104" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N104" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14218,7 +14237,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14236,21 +14255,21 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14270,18 +14289,20 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>567</v>
+        <v>347</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>568</v>
+        <v>348</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14330,7 +14351,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>566</v>
+        <v>351</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14348,21 +14369,21 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>570</v>
+        <v>352</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14385,13 +14406,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14418,13 +14439,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14442,7 +14463,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14466,15 +14487,15 @@
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14497,13 +14518,13 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14530,14 +14551,14 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>582</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
       </c>
@@ -14554,7 +14575,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14572,7 +14593,7 @@
         <v>81</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>107</v>
+        <v>582</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
@@ -14597,7 +14618,7 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
@@ -14609,7 +14630,7 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>585</v>
@@ -14617,12 +14638,8 @@
       <c r="M108" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="N108" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>588</v>
-      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -14649,10 +14666,10 @@
         <v>159</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -14676,7 +14693,7 @@
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>81</v>
@@ -14688,21 +14705,21 @@
         <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>591</v>
+        <v>107</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14725,16 +14742,20 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O109" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -14758,14 +14779,14 @@
         <v>81</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>81</v>
       </c>
@@ -14782,7 +14803,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14800,21 +14821,21 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>599</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14837,13 +14858,13 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14873,11 +14894,11 @@
         <v>173</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
       </c>
@@ -14894,7 +14915,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14912,21 +14933,21 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14937,7 +14958,7 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>81</v>
@@ -14949,13 +14970,13 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>567</v>
+        <v>255</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14982,13 +15003,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>81</v>
+        <v>609</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15006,13 +15027,13 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>81</v>
@@ -15024,21 +15045,21 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15061,13 +15082,13 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15094,11 +15115,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15116,7 +15139,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15162,7 +15185,7 @@
         <v>89</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>81</v>
@@ -15171,7 +15194,7 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>619</v>
@@ -15179,9 +15202,7 @@
       <c r="M113" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>621</v>
-      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15206,13 +15227,11 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>81</v>
+        <v>621</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15236,7 +15255,7 @@
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
@@ -15254,15 +15273,15 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>81</v>
+        <v>623</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15276,7 +15295,7 @@
         <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>81</v>
@@ -15285,15 +15304,17 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>104</v>
+        <v>625</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15342,25 +15363,25 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>106</v>
+        <v>624</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>107</v>
+        <v>628</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>81</v>
@@ -15371,21 +15392,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
@@ -15397,17 +15418,15 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -15456,19 +15475,19 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>81</v>
@@ -15485,14 +15504,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15505,26 +15524,24 @@
         <v>81</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O116" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -15572,7 +15589,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15590,7 +15607,7 @@
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>81</v>
@@ -15601,42 +15618,46 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>627</v>
+        <v>110</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>628</v>
+        <v>373</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -15684,39 +15705,39 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>626</v>
+        <v>375</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>630</v>
+        <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>474</v>
+        <v>192</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>631</v>
+        <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>632</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15724,7 +15745,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>89</v>
@@ -15739,7 +15760,7 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>169</v>
+        <v>633</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>634</v>
@@ -15747,9 +15768,7 @@
       <c r="M118" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N118" t="s" s="2">
-        <v>636</v>
-      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -15774,13 +15793,13 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>638</v>
+        <v>81</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -15798,10 +15817,10 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>89</v>
@@ -15813,24 +15832,24 @@
         <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>81</v>
+        <v>636</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>639</v>
+        <v>480</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>81</v>
+        <v>638</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15853,16 +15872,16 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15888,9 +15907,11 @@
         <v>81</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y119" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="Z119" t="s" s="2">
         <v>644</v>
       </c>
@@ -15910,7 +15931,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15928,7 +15949,7 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>81</v>
+        <v>645</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
@@ -15939,10 +15960,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15965,15 +15986,17 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>333</v>
+        <v>255</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -15998,13 +16021,11 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>81</v>
+        <v>650</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
@@ -16022,7 +16043,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16040,7 +16061,7 @@
         <v>81</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16051,10 +16072,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16080,10 +16101,10 @@
         <v>340</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16134,7 +16155,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16149,24 +16170,24 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL121" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>652</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16189,7 +16210,7 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>654</v>
+        <v>347</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>655</v>
@@ -16197,9 +16218,7 @@
       <c r="M122" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N122" t="s" s="2">
-        <v>657</v>
-      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16248,7 +16267,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16263,20 +16282,134 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AL122" t="s" s="2">
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AM122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN122" t="s" s="2">
+      <c r="B123" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN122">
+  <autoFilter ref="A1:AN123">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16286,7 +16419,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI121">
+  <conditionalFormatting sqref="A2:AI122">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$121</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4438" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -697,38 +697,6 @@
   </si>
   <si>
     <t>Statut de pré-admission</t>
-  </si>
-  <si>
-    <t>Encounter.extension:consentements</t>
-  </si>
-  <si>
-    <t>consentements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-extension}
-</t>
-  </si>
-  <si>
-    <t>Consentements</t>
-  </si>
-  <si>
-    <t>Consentement lié à la préadmission</t>
-  </si>
-  <si>
-    <t>Encounter.extension:questionnaire</t>
-  </si>
-  <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
-</t>
-  </si>
-  <si>
-    <t>Questionnaire libre lié à la préadmission</t>
-  </si>
-  <si>
-    <t>Référence vers un ou plusieurs QuestionnaireResponse remplis dans le cadre de la préadmission.</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2400,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN123"/>
+  <dimension ref="A1:AN121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.34765625" customWidth="true" bestFit="true"/>
@@ -4957,13 +4925,11 @@
         <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4976,22 +4942,26 @@
         <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -5039,7 +5009,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5057,7 +5027,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -5071,17 +5041,15 @@
         <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>80</v>
@@ -5093,16 +5061,16 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5153,7 +5121,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5165,63 +5133,59 @@
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -5269,25 +5233,25 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5298,18 +5262,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>80</v>
@@ -5321,18 +5285,20 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5369,19 +5335,19 @@
         <v>81</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5393,27 +5359,27 @@
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>107</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5430,22 +5396,26 @@
         <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5454,7 +5424,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -5469,13 +5439,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5493,7 +5463,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>106</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5505,38 +5475,38 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5545,21 +5515,23 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5583,63 +5555,61 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>117</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5656,26 +5626,22 @@
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>104</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5684,7 +5650,7 @@
         <v>81</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>81</v>
@@ -5699,13 +5665,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5723,7 +5689,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>252</v>
+        <v>106</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5735,19 +5701,19 @@
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5759,14 +5725,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5775,23 +5741,21 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5815,61 +5779,63 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5880,7 +5846,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5889,19 +5855,23 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5949,50 +5919,50 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -6004,17 +5974,15 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6051,31 +6019,31 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -6092,14 +6060,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6115,23 +6083,21 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
+        <v>112</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6167,19 +6133,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6191,27 +6157,27 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6231,19 +6197,23 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6267,13 +6237,11 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6291,7 +6259,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6303,38 +6271,38 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6343,19 +6311,19 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6393,51 +6361,51 @@
         <v>81</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>117</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>107</v>
+        <v>278</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6460,19 +6428,17 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6482,7 +6448,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6497,11 +6463,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6519,7 +6487,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6537,21 +6505,21 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6577,15 +6545,15 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6633,7 +6601,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6651,21 +6619,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6688,17 +6656,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6708,7 +6678,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6747,7 +6717,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6765,21 +6735,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6805,14 +6775,16 @@
         <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6861,7 +6833,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6879,21 +6851,21 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6901,7 +6873,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6916,19 +6888,19 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6941,7 +6913,7 @@
         <v>81</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>81</v>
@@ -6977,7 +6949,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6995,21 +6967,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7017,7 +6989,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -7035,17 +7007,15 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7057,7 +7027,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7093,7 +7063,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7111,21 +7081,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7133,7 +7103,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -7148,20 +7118,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>330</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7173,7 +7139,7 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>81</v>
@@ -7209,7 +7175,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7227,21 +7193,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7249,7 +7215,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -7264,16 +7230,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>337</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7287,7 +7253,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7323,7 +7289,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7341,21 +7307,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7363,30 +7329,32 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7411,13 +7379,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7435,10 +7403,10 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7450,24 +7418,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>352</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7478,7 +7446,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7487,19 +7455,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7549,13 +7517,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7567,21 +7535,21 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7589,32 +7557,30 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7639,13 +7605,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7663,10 +7629,10 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>89</v>
@@ -7675,31 +7641,31 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>361</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7718,16 +7684,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>368</v>
+        <v>113</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7777,7 +7743,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7789,7 +7755,7 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7806,42 +7772,46 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7889,25 +7859,25 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7918,21 +7888,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7944,17 +7914,15 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>111</v>
+        <v>345</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7979,13 +7947,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8003,19 +7971,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>117</v>
+        <v>366</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -8032,46 +8000,42 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8119,25 +8083,25 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -8148,10 +8112,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8165,22 +8129,22 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8207,13 +8171,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>249</v>
+        <v>151</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8231,7 +8195,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8249,21 +8213,21 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>375</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8271,7 +8235,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8286,13 +8250,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>105</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8343,10 +8307,10 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>106</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -8355,7 +8319,7 @@
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8372,41 +8336,43 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>111</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8431,63 +8397,63 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>117</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>385</v>
+        <v>107</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8495,7 +8461,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8507,19 +8473,23 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8567,7 +8537,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8579,38 +8549,38 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8619,19 +8589,19 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8669,51 +8639,51 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>117</v>
+        <v>277</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>107</v>
+        <v>278</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8736,19 +8706,17 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8773,13 +8741,11 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8797,7 +8763,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8815,21 +8781,21 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8855,15 +8821,15 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8911,7 +8877,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8929,21 +8895,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8951,7 +8917,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8966,17 +8932,19 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9001,11 +8969,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9023,7 +8993,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9041,21 +9011,21 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9066,7 +9036,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -9075,21 +9045,19 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>355</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>301</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9137,13 +9105,13 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>302</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
@@ -9155,21 +9123,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>303</v>
+        <v>107</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9189,23 +9157,19 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>307</v>
+        <v>104</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9253,7 +9217,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>106</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9265,31 +9229,31 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9308,15 +9272,17 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9365,7 +9331,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>117</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9377,7 +9343,7 @@
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9394,42 +9360,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9477,25 +9447,25 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -9506,21 +9476,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9532,17 +9502,15 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>111</v>
+        <v>393</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9567,13 +9535,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9591,19 +9559,19 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>117</v>
+        <v>392</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -9620,46 +9588,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9707,25 +9671,25 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
@@ -9736,10 +9700,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9747,7 +9711,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>
@@ -9759,18 +9723,20 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9795,13 +9761,11 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9819,13 +9783,13 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
@@ -9834,24 +9798,24 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>107</v>
+        <v>404</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9859,7 +9823,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9871,16 +9835,16 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>340</v>
+        <v>245</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9907,13 +9871,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9931,10 +9895,10 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -9946,7 +9910,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>107</v>
@@ -9955,15 +9919,15 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9983,20 +9947,18 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10023,33 +9985,35 @@
       <c r="X67" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="Y67" s="2"/>
+      <c r="Y67" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="Z67" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -10058,28 +10022,28 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10098,15 +10062,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>255</v>
+        <v>421</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10131,31 +10097,31 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10170,24 +10136,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10198,7 +10164,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10207,16 +10173,16 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>255</v>
+        <v>430</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10243,13 +10209,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10267,13 +10233,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10282,35 +10248,35 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>426</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10319,20 +10285,18 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10381,13 +10345,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -10396,24 +10360,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10427,7 +10391,7 @@
         <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>81</v>
@@ -10436,13 +10400,13 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>440</v>
+        <v>355</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10493,7 +10457,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10508,35 +10472,35 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>107</v>
+        <v>447</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10548,13 +10512,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>448</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>449</v>
+        <v>104</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>450</v>
+        <v>105</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10605,25 +10569,25 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>452</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10634,14 +10598,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10651,24 +10615,26 @@
         <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -10717,7 +10683,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10729,59 +10695,63 @@
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>457</v>
+        <v>107</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>458</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10829,25 +10799,25 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10858,14 +10828,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10881,19 +10851,19 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>112</v>
+        <v>454</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>113</v>
+        <v>455</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10919,13 +10889,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -10943,7 +10913,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>117</v>
+        <v>452</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10955,63 +10925,59 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>373</v>
+        <v>461</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11059,39 +11025,39 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>192</v>
+        <v>463</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11102,7 +11068,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11114,17 +11080,15 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>255</v>
+        <v>466</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11149,13 +11113,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11173,13 +11137,13 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
@@ -11188,24 +11152,24 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11225,16 +11189,16 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>340</v>
+        <v>474</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11285,13 +11249,13 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11300,24 +11264,24 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11325,30 +11289,32 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>476</v>
+        <v>330</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11397,7 +11363,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11412,24 +11378,24 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11449,18 +11415,20 @@
         <v>81</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11509,13 +11477,13 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>81</v>
@@ -11524,56 +11492,56 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>81</v>
+        <v>495</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K81" t="s" s="2">
-        <v>340</v>
+        <v>245</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11599,13 +11567,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11623,13 +11591,13 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>81</v>
@@ -11638,35 +11606,35 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>495</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -11675,19 +11643,19 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11737,13 +11705,13 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
@@ -11752,28 +11720,28 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>502</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11792,17 +11760,15 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>255</v>
+        <v>355</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11827,13 +11793,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11851,7 +11817,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11866,35 +11832,35 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AL83" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AM83" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>514</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -11903,20 +11869,18 @@
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>103</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>104</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11965,43 +11929,43 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>106</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>512</v>
+        <v>107</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>514</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12017,18 +11981,20 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>519</v>
+        <v>111</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12077,7 +12043,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>117</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12089,13 +12055,13 @@
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>521</v>
+        <v>107</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -12106,42 +12072,46 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12189,25 +12159,25 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -12218,21 +12188,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>516</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12241,19 +12211,19 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>517</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>518</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
+        <v>498</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12303,75 +12273,71 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>515</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>81</v>
+        <v>520</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>107</v>
+        <v>521</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>81</v>
+        <v>522</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>373</v>
+        <v>524</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12395,13 +12361,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>527</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12419,25 +12385,25 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -12448,18 +12414,18 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>89</v>
@@ -12471,20 +12437,18 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12533,10 +12497,10 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>89</v>
@@ -12548,16 +12512,16 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -12588,15 +12552,17 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>255</v>
+        <v>534</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -12621,13 +12587,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12651,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>81</v>
@@ -12663,7 +12629,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>107</v>
+        <v>538</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12674,10 +12640,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12700,7 +12666,7 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>539</v>
+        <v>355</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>540</v>
@@ -12708,7 +12674,9 @@
       <c r="M91" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N91" s="2"/>
+      <c r="N91" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -12757,7 +12725,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12775,7 +12743,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12786,10 +12754,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12812,17 +12780,15 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>544</v>
+        <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>545</v>
+        <v>104</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -12871,25 +12837,25 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>543</v>
+        <v>106</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>548</v>
+        <v>107</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -12900,21 +12866,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -12926,16 +12892,16 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>550</v>
+        <v>111</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>551</v>
+        <v>112</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>552</v>
+        <v>113</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12985,25 +12951,25 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>549</v>
+        <v>117</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>553</v>
+        <v>107</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -13014,42 +12980,46 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -13097,25 +13067,25 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -13126,21 +13096,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -13152,17 +13122,15 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>548</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13211,75 +13179,71 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>547</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>81</v>
+        <v>550</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13327,25 +13291,25 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>375</v>
+        <v>106</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13356,21 +13320,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
@@ -13382,15 +13346,17 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>234</v>
+        <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>558</v>
+        <v>111</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13427,51 +13393,51 @@
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>557</v>
+        <v>117</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>238</v>
+        <v>107</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>560</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13488,22 +13454,26 @@
         <v>81</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13527,13 +13497,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -13551,7 +13521,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>106</v>
+        <v>242</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13563,38 +13533,38 @@
         <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>
@@ -13603,21 +13573,23 @@
         <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>112</v>
+        <v>555</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -13641,63 +13613,61 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>117</v>
+        <v>251</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13705,7 +13675,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>89</v>
@@ -13714,38 +13684,38 @@
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>245</v>
+        <v>557</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>81</v>
+        <v>558</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>81</v>
@@ -13757,13 +13727,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -13781,7 +13751,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13799,21 +13769,21 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>192</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13836,20 +13806,18 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>255</v>
+        <v>103</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>565</v>
+        <v>323</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -13861,7 +13829,7 @@
         <v>81</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>81</v>
@@ -13873,11 +13841,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -13895,7 +13865,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>261</v>
+        <v>326</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13913,21 +13883,21 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>262</v>
+        <v>328</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13935,7 +13905,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -13950,32 +13920,28 @@
         <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>131</v>
+        <v>330</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>81</v>
@@ -14011,7 +13977,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14029,21 +13995,21 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14051,7 +14017,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14066,16 +14032,16 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>337</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14089,7 +14055,7 @@
         <v>81</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>81</v>
@@ -14125,7 +14091,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14143,21 +14109,21 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14177,16 +14143,16 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>340</v>
+        <v>563</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>341</v>
+        <v>564</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>342</v>
+        <v>565</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14237,7 +14203,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>343</v>
+        <v>562</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14255,21 +14221,21 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>344</v>
+        <v>566</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>345</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14289,20 +14255,18 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>347</v>
+        <v>245</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>348</v>
+        <v>568</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14327,13 +14291,13 @@
         <v>81</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>81</v>
+        <v>571</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>81</v>
@@ -14351,7 +14315,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>351</v>
+        <v>567</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14369,21 +14333,21 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>352</v>
+        <v>572</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>353</v>
+        <v>573</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14406,13 +14370,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>573</v>
+        <v>245</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14439,13 +14403,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14463,7 +14427,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14481,21 +14445,21 @@
         <v>81</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>576</v>
+        <v>107</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>81</v>
+        <v>579</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14506,7 +14470,7 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>81</v>
@@ -14518,16 +14482,20 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -14551,37 +14519,37 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>81</v>
@@ -14593,21 +14561,21 @@
         <v>81</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14618,7 +14586,7 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
@@ -14630,13 +14598,13 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14663,13 +14631,13 @@
         <v>81</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -14687,13 +14655,13 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>81</v>
@@ -14705,21 +14673,21 @@
         <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>107</v>
+        <v>594</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14742,20 +14710,16 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -14779,31 +14743,31 @@
         <v>81</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="Z109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14821,21 +14785,21 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14846,7 +14810,7 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>81</v>
@@ -14858,13 +14822,13 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>255</v>
+        <v>563</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14891,37 +14855,37 @@
         <v>81</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>602</v>
+        <v>81</v>
       </c>
       <c r="Z110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AA110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>81</v>
@@ -14933,21 +14897,21 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14958,7 +14922,7 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>81</v>
@@ -14970,13 +14934,13 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15003,13 +14967,11 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15027,13 +14989,13 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>81</v>
@@ -15045,21 +15007,21 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15070,7 +15032,7 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>81</v>
@@ -15082,15 +15044,17 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>573</v>
+        <v>355</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15139,13 +15103,13 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>81</v>
@@ -15157,21 +15121,21 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>617</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15194,13 +15158,13 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>255</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>619</v>
+        <v>104</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>620</v>
+        <v>105</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15227,11 +15191,13 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>621</v>
+        <v>81</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15249,7 +15215,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>618</v>
+        <v>106</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15261,41 +15227,41 @@
         <v>81</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>622</v>
+        <v>107</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>623</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>81</v>
@@ -15304,16 +15270,16 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>625</v>
+        <v>111</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>626</v>
+        <v>112</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>627</v>
+        <v>113</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15363,7 +15329,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>624</v>
+        <v>117</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15375,13 +15341,13 @@
         <v>81</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>628</v>
+        <v>107</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>81</v>
@@ -15392,42 +15358,46 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -15475,25 +15445,25 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>81</v>
@@ -15504,21 +15474,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>81</v>
@@ -15530,17 +15500,15 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>110</v>
+        <v>623</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>111</v>
+        <v>624</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -15589,75 +15557,73 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>117</v>
+        <v>622</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>81</v>
+        <v>626</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>107</v>
+        <v>470</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>81</v>
+        <v>627</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>81</v>
+        <v>628</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>373</v>
+        <v>630</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>374</v>
+        <v>631</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -15681,13 +15647,13 @@
         <v>81</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>81</v>
+        <v>633</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>81</v>
+        <v>634</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -15705,25 +15671,25 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>375</v>
+        <v>629</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>192</v>
+        <v>635</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>81</v>
@@ -15734,10 +15700,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15745,7 +15711,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>89</v>
@@ -15760,15 +15726,17 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>633</v>
+        <v>245</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>638</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -15793,13 +15761,11 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>81</v>
+        <v>640</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -15817,10 +15783,10 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>89</v>
@@ -15832,24 +15798,24 @@
         <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>636</v>
+        <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>638</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15872,17 +15838,15 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -15907,13 +15871,13 @@
         <v>81</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>643</v>
+        <v>81</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -15931,7 +15895,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15949,7 +15913,7 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>645</v>
+        <v>463</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
@@ -15960,10 +15924,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15986,17 +15950,15 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>255</v>
+        <v>337</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16021,11 +15983,13 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>650</v>
+        <v>81</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
@@ -16043,7 +16007,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16058,24 +16022,24 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>81</v>
+        <v>647</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>81</v>
+        <v>648</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16098,15 +16062,17 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>340</v>
+        <v>650</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16155,7 +16121,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16170,246 +16136,20 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>81</v>
+        <v>654</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>473</v>
+        <v>655</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN123">
+  <autoFilter ref="A1:AN121">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16419,7 +16159,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI120">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1319,7 +1319,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-encounter-fr.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>Encounter.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,6 +472,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
+  </si>
+  <si>
     <t>Encounter.meta.security</t>
   </si>
   <si>
@@ -494,7 +497,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +521,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +564,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -637,7 +640,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -798,64 +801,67 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1062,7 +1068,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1177,7 +1183,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1261,7 +1267,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1285,7 +1291,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1300,7 +1306,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1347,7 +1353,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1373,7 +1379,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1428,7 +1434,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1458,7 +1464,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1564,7 +1570,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1582,7 +1588,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1617,7 +1623,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1648,7 +1654,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1670,7 +1676,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1761,7 +1767,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1786,7 +1792,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1807,7 +1813,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1831,7 +1837,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1852,7 +1858,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1873,7 +1879,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1906,7 +1912,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1942,7 +1948,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1995,7 +2001,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -2025,7 +2031,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -2381,7 +2387,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.0078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2396,7 +2402,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.76171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3604,7 +3610,7 @@
         <v>81</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>81</v>
@@ -3672,10 +3678,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3698,16 +3704,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3733,13 +3739,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3757,7 +3763,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3786,10 +3792,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3812,16 +3818,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3847,13 +3853,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3871,7 +3877,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3900,10 +3906,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3929,13 +3935,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3985,7 +3991,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4014,10 +4020,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4040,16 +4046,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4075,13 +4081,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4099,7 +4105,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4128,14 +4134,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4154,16 +4160,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4213,7 +4219,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4231,7 +4237,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -4242,14 +4248,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4268,16 +4274,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4327,7 +4333,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4345,7 +4351,7 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -4356,10 +4362,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4385,10 +4391,10 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4437,7 +4443,7 @@
         <v>116</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4466,13 +4472,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4494,13 +4500,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4551,7 +4557,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4560,7 +4566,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
@@ -4580,13 +4586,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>81</v>
@@ -4608,13 +4614,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4665,7 +4671,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4694,13 +4700,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>81</v>
@@ -4722,13 +4728,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4779,7 +4785,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4808,13 +4814,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
@@ -4836,13 +4842,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4893,7 +4899,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4922,10 +4928,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4951,16 +4957,16 @@
         <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5009,7 +5015,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5027,7 +5033,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -5038,10 +5044,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5064,13 +5070,13 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5121,7 +5127,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5136,24 +5142,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5262,10 +5268,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5376,10 +5382,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5402,19 +5408,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5424,7 +5430,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -5439,13 +5445,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5463,7 +5469,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5481,21 +5487,21 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5518,19 +5524,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5555,11 +5561,11 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5577,7 +5583,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5595,21 +5601,21 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5718,10 +5724,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5832,10 +5838,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5858,19 +5864,19 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5919,7 +5925,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5937,21 +5943,21 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6060,10 +6066,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6174,10 +6180,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6203,16 +6209,16 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6237,11 +6243,11 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6259,7 +6265,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6277,21 +6283,21 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6317,13 +6323,13 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6373,7 +6379,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6391,21 +6397,21 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6428,17 +6434,17 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6448,7 +6454,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6487,7 +6493,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6505,21 +6511,21 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6545,14 +6551,14 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6601,7 +6607,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6619,21 +6625,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6656,19 +6662,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6717,7 +6723,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6735,21 +6741,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6775,16 +6781,16 @@
         <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6833,7 +6839,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6851,21 +6857,21 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6891,16 +6897,16 @@
         <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6913,7 +6919,7 @@
         <v>81</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>81</v>
@@ -6949,7 +6955,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6967,21 +6973,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7007,13 +7013,13 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7027,7 +7033,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7063,7 +7069,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7081,21 +7087,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7118,13 +7124,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7175,7 +7181,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7193,21 +7199,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7230,16 +7236,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7289,7 +7295,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7307,21 +7313,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7344,16 +7350,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7379,13 +7385,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7403,7 +7409,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>89</v>
@@ -7418,24 +7424,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7458,16 +7464,16 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7517,7 +7523,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7546,10 +7552,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7658,10 +7664,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7772,14 +7778,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7801,16 +7807,16 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7859,7 +7865,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7877,7 +7883,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7888,10 +7894,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7914,13 +7920,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7947,13 +7953,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7971,7 +7977,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -8000,10 +8006,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8026,13 +8032,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8083,7 +8089,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -8112,10 +8118,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8138,13 +8144,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8171,13 +8177,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8195,7 +8201,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8213,21 +8219,21 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8336,10 +8342,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8450,10 +8456,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8479,16 +8485,16 @@
         <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8537,7 +8543,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8555,21 +8561,21 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8595,13 +8601,13 @@
         <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8651,7 +8657,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8669,21 +8675,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8706,17 +8712,17 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8741,11 +8747,11 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8763,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8781,21 +8787,21 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8821,14 +8827,14 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8877,7 +8883,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8895,21 +8901,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8932,19 +8938,19 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8993,7 +8999,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9011,21 +9017,21 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9048,13 +9054,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9105,7 +9111,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9134,10 +9140,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9246,10 +9252,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9360,14 +9366,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9389,16 +9395,16 @@
         <v>110</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9447,7 +9453,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9465,7 +9471,7 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -9476,10 +9482,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9502,13 +9508,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9535,13 +9541,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9559,7 +9565,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>89</v>
@@ -9588,10 +9594,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9614,13 +9620,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9671,7 +9677,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9700,10 +9706,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9714,7 +9720,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9726,16 +9732,16 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9761,11 +9767,11 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9783,7 +9789,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9798,24 +9804,24 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9838,13 +9844,13 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9871,13 +9877,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9895,7 +9901,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9910,7 +9916,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>107</v>
@@ -9919,15 +9925,15 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9950,13 +9956,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9983,31 +9989,31 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10025,25 +10031,25 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10062,16 +10068,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10121,7 +10127,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10136,24 +10142,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10176,13 +10182,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10233,7 +10239,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10248,28 +10254,28 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10288,13 +10294,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10345,7 +10351,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10360,10 +10366,10 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -10374,10 +10380,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10400,13 +10406,13 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10457,7 +10463,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10472,24 +10478,24 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10598,10 +10604,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10712,14 +10718,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10741,16 +10747,16 @@
         <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10799,7 +10805,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10817,7 +10823,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10828,10 +10834,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10854,16 +10860,16 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10889,31 +10895,31 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10928,24 +10934,24 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10968,13 +10974,13 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11025,7 +11031,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11043,21 +11049,21 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11080,13 +11086,13 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11137,7 +11143,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11152,24 +11158,24 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11192,13 +11198,13 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11249,7 +11255,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11264,24 +11270,24 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11304,16 +11310,16 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11363,7 +11369,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11378,24 +11384,24 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11418,16 +11424,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11477,7 +11483,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11492,28 +11498,28 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11532,16 +11538,16 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11567,13 +11573,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11591,7 +11597,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11606,28 +11612,28 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11646,16 +11652,16 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11705,7 +11711,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11720,24 +11726,24 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11760,13 +11766,13 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11817,7 +11823,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11835,7 +11841,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -11846,10 +11852,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11958,10 +11964,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12072,14 +12078,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12101,16 +12107,16 @@
         <v>110</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -12159,7 +12165,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12177,7 +12183,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -12188,14 +12194,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12214,16 +12220,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12273,7 +12279,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>89</v>
@@ -12288,24 +12294,24 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12328,13 +12334,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12361,13 +12367,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12385,7 +12391,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12414,10 +12420,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12440,13 +12446,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12497,7 +12503,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12515,7 +12521,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -12526,10 +12532,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12552,16 +12558,16 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12611,7 +12617,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12629,7 +12635,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12640,10 +12646,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12666,16 +12672,16 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12725,7 +12731,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12743,7 +12749,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12754,10 +12760,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12866,10 +12872,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12980,14 +12986,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13009,16 +13015,16 @@
         <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13067,7 +13073,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13085,7 +13091,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -13096,10 +13102,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13122,13 +13128,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13179,7 +13185,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13197,21 +13203,21 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13320,10 +13326,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13434,10 +13440,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13460,19 +13466,19 @@
         <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13497,13 +13503,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -13521,7 +13527,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13539,21 +13545,21 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13576,19 +13582,19 @@
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -13613,11 +13619,11 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -13635,7 +13641,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13653,21 +13659,21 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13693,29 +13699,29 @@
         <v>131</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>81</v>
@@ -13751,7 +13757,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13769,21 +13775,21 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13809,13 +13815,13 @@
         <v>103</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13829,7 +13835,7 @@
         <v>81</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>81</v>
@@ -13865,7 +13871,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13883,21 +13889,21 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13920,13 +13926,13 @@
         <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13977,7 +13983,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13995,21 +14001,21 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14032,16 +14038,16 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14091,7 +14097,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14109,21 +14115,21 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14146,13 +14152,13 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14203,7 +14209,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14221,7 +14227,7 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
@@ -14232,10 +14238,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14258,13 +14264,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14291,13 +14297,13 @@
         <v>81</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>81</v>
@@ -14315,7 +14321,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14333,21 +14339,21 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14370,13 +14376,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14403,13 +14409,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14427,7 +14433,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14451,15 +14457,15 @@
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14482,19 +14488,19 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -14519,13 +14525,13 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14543,7 +14549,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14561,21 +14567,21 @@
         <v>81</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14598,13 +14604,13 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14631,13 +14637,13 @@
         <v>81</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -14655,7 +14661,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14673,21 +14679,21 @@
         <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14710,13 +14716,13 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14743,13 +14749,13 @@
         <v>81</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>81</v>
@@ -14767,7 +14773,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14785,21 +14791,21 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14822,13 +14828,13 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14879,7 +14885,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14897,21 +14903,21 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14934,13 +14940,13 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14967,11 +14973,11 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -14989,7 +14995,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15007,21 +15013,21 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15044,16 +15050,16 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15103,7 +15109,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15121,7 +15127,7 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>81</v>
@@ -15132,10 +15138,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15244,10 +15250,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15358,14 +15364,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15387,16 +15393,16 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -15445,7 +15451,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15463,7 +15469,7 @@
         <v>81</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>81</v>
@@ -15474,10 +15480,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15500,13 +15506,13 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15557,7 +15563,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>89</v>
@@ -15572,24 +15578,24 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15612,16 +15618,16 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15647,13 +15653,13 @@
         <v>81</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -15671,7 +15677,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15689,7 +15695,7 @@
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>81</v>
@@ -15700,10 +15706,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15726,16 +15732,16 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15761,11 +15767,11 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -15783,7 +15789,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15812,10 +15818,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15838,13 +15844,13 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15895,7 +15901,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15913,7 +15919,7 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
@@ -15924,10 +15930,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15950,13 +15956,13 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16007,7 +16013,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16022,24 +16028,24 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16062,16 +16068,16 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16121,7 +16127,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16136,10 +16142,10 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
